--- a/GUI/timetablingTemplate.xlsx
+++ b/GUI/timetablingTemplate.xlsx
@@ -8,11 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="corsi" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="aule" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="disponibilitàProfessori" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="disponibilitàAule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="disponibilitàScdla" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="configurazione" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="disponibilitàProfessori" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="disponibilitàAule" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="disponibilitàGruppiStudenti" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="configurazione" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -418,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,7 +438,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>studentiCorsoDiLaureaAnno scdla</t>
+          <t>gruppoStudenti</t>
         </is>
       </c>
     </row>
@@ -450,7 +449,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -466,40 +465,140 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>analisi</t>
+          <t>analisi2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Marcellini</t>
+          <t>Kovarik</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ITID1</t>
+          <t>ITID3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>componenti</t>
+          <t>sistemiDiMisura</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bau</t>
+          <t>Serpelloni</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>ITID3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>robotica</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Tampalini</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ITID3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cybersecurity</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Gringoli</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ITID3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>elettronicaGenerale</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Flammini</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Informatica3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sistemiOperativi</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Baroni</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Informatica3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LaboratorioRasperry</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sisinni</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Informatica3</t>
         </is>
       </c>
     </row>
@@ -514,44 +613,1666 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:BD9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>aula</t>
+          <t>professore</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>capienza?</t>
+          <t>mon08</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>mon09</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>mon10</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>mon11</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>mon12</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>mon13</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>mon14</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>mon15</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>mon16</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>mon17</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>mon18</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>tue08</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>tue09</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>tue10</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>tue11</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>tue12</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>tue13</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>tue14</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>tue15</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>tue16</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>tue17</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>tue18</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>wed08</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>wed09</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>wed10</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>wed11</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>wed12</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>wed13</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>wed14</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>wed15</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>wed16</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>wed17</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>wed18</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>thu08</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>thu09</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>thu10</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>thu11</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>thu12</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>thu13</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>thu14</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>thu15</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>thu16</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>thu17</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>thu18</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>fri08</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>fri09</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>fri10</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>fri11</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>fri12</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>fri13</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>fri14</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>fri15</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>fri16</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>fri17</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>fri18</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N6</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>Sisinni</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>Kovarik</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B31</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>Bau</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Serpelloni</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tampalini</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gringoli</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Flammini</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Baroni</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -564,13 +2285,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD4"/>
+  <dimension ref="A1:BD5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>professore</t>
+          <t>aula</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -852,213 +2573,213 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sisinni</t>
+          <t>N6</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marcellini</t>
+          <t>N3</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
@@ -1094,176 +2815,176 @@
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bau</t>
+          <t>B31</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
         <v>1</v>
@@ -1299,70 +3020,242 @@
         <v>1</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CaNoa</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1376,13 +3269,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD4"/>
+  <dimension ref="A1:BD3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>aula</t>
+          <t>gruppiStudenti</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -1664,41 +3557,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N6</t>
+          <t>ITID3</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -1713,197 +3606,197 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>Informatica3</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
         <v>1</v>
@@ -1912,13 +3805,13 @@
         <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC3" t="n">
         <v>1</v>
@@ -1939,242 +3832,70 @@
         <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>B31</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2188,726 +3909,98 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD3"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>scdla</t>
+          <t>configurazioni</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>mon08</t>
+          <t>valori</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>mon09</t>
+          <t>Unnamed: 2</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>mon10</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>mon11</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>mon12</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>mon13</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>mon14</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>mon15</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>mon16</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>mon17</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>mon18</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>tue08</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>tue09</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>tue10</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>tue11</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>tue12</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>tue13</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>tue14</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>tue15</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>tue16</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>tue17</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>tue18</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>wed08</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>wed09</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>wed10</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>wed11</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>wed12</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>wed13</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>wed14</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>wed15</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>wed16</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>wed17</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>wed18</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>thu08</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>thu09</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>thu10</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>thu11</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>thu12</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>thu13</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>thu14</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>thu15</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>thu16</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>thu17</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>thu18</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>fri08</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>fri09</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>fri10</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
-        <is>
-          <t>fri11</t>
-        </is>
-      </c>
-      <c r="AX1" t="inlineStr">
-        <is>
-          <t>fri12</t>
-        </is>
-      </c>
-      <c r="AY1" t="inlineStr">
-        <is>
-          <t>fri13</t>
-        </is>
-      </c>
-      <c r="AZ1" t="inlineStr">
-        <is>
-          <t>fri14</t>
-        </is>
-      </c>
-      <c r="BA1" t="inlineStr">
-        <is>
-          <t>fri15</t>
-        </is>
-      </c>
-      <c r="BB1" t="inlineStr">
-        <is>
-          <t>fri16</t>
-        </is>
-      </c>
-      <c r="BC1" t="inlineStr">
-        <is>
-          <t>fri17</t>
-        </is>
-      </c>
-      <c r="BD1" t="inlineStr">
-        <is>
-          <t>fri18</t>
+          <t>Unnamed: 3</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ITID1</t>
+          <t>ora pausa pranzo</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ITID3</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>configurazioni</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>valori</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Unnamed: 2</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Unnamed: 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>orario a costo minimo</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>8</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>DA IMPLEMENTARE</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>orario nel quale inserire un ora di pausa pranzo</t>
+          <t>orario a costo minimo</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>DA IMPLEMENTARE</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>fascia oraria singola magari non è una buona cosa eliminarla</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>valorizzare il tenere le giornate vuote?</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+          <t>orario nel quale inserire un ora di pausa pranzo</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DA IMPLEMENTARE</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>fascia oraria singola magari non è una buona cosa eliminarla</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>valorizzare il tenere le mezze giornate vuote?</t>
+          <t>valorizzare il tenere le giornate vuote?</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>valorizzare il tenere le mezze giornate vuote?</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
